--- a/夢通信_2026年09月号.xlsx
+++ b/夢通信_2026年09月号.xlsx
@@ -71,15 +71,40 @@
   </si>
   <si>
     <t xml:space="preserve">秋の自然観察</t>
+    <rPh sb="0" eb="1">
+      <t>あき</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>しぜん</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>かんさつ</t>
+    </rPh>
+    <phoneticPr fontId="16" type="Hiragana" alignment="distributed"/>
   </si>
   <si>
     <t xml:space="preserve">アスレチック公園</t>
+    <rPh sb="6" eb="8">
+      <t>こうえん</t>
+    </rPh>
+    <phoneticPr fontId="16" type="Hiragana" alignment="distributed"/>
   </si>
   <si>
     <t xml:space="preserve">ボッチャ大会</t>
+    <rPh sb="4" eb="6">
+      <t>たいかい</t>
+    </rPh>
+    <phoneticPr fontId="16" type="Hiragana" alignment="distributed"/>
   </si>
   <si>
     <t xml:space="preserve">芋掘り</t>
+    <rPh sb="0" eb="1">
+      <t>いも</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ほ</t>
+    </rPh>
+    <phoneticPr fontId="16" type="Hiragana" alignment="distributed"/>
   </si>
   <si>
     <t>防災週間</t>
@@ -93,19 +118,48 @@
   </si>
   <si>
     <t xml:space="preserve">リズム遊び週間</t>
+    <rPh sb="3" eb="4">
+      <t>あそ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>しゅうかん</t>
+    </rPh>
+    <phoneticPr fontId="16" type="Hiragana" alignment="distributed"/>
   </si>
   <si>
     <t xml:space="preserve">お月見会</t>
+    <rPh sb="1" eb="3">
+      <t>つきみ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>かい</t>
+    </rPh>
+    <phoneticPr fontId="16" type="Hiragana" alignment="distributed"/>
   </si>
   <si>
     <t xml:space="preserve">敬老の日
 プレゼント作り週間</t>
+    <rPh sb="0" eb="2">
+      <t>けいろう</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ひ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>つく</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>しゅうかん</t>
+    </rPh>
+    <phoneticPr fontId="16" type="Hiragana" alignment="distributed"/>
   </si>
   <si>
     <t xml:space="preserve">日頃より夢門塾ゆうゆう日吉をご利用いただき誠にありがとうございます。朝晩は過ごしやすくなり、秋の気配が感じられる季節になりました。気温差で体調を崩さないよう、体調第一で過ごしましょう！</t>
+    <phoneticPr fontId="16" type="Hiragana" alignment="distributed"/>
   </si>
   <si>
     <t xml:space="preserve">おはぎづくり</t>
+    <phoneticPr fontId="16" type="Hiragana" alignment="distributed"/>
   </si>
 </sst>
 </file>
@@ -3249,33 +3303,21 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="20" name="図 19">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId id="{21F309A4-C411-2925-1CEC-DBF8E0DE2BAA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="100" name="秋装飾ヘッダー"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId5" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
+        <a:blip r:embed="rId34" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5452578" y="554007"/>
-          <a:ext cx="894182" cy="681944"/>
+          <a:off x="0" y="0"/>
+          <a:ext cx="500000" cy="400000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3299,33 +3341,21 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="図 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId id="{68B0C7E7-F174-4D33-8087-18F34372D6FE}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="101" name="秋装飾_紅葉"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId19" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
+        <a:blip r:embed="rId35" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="644594" y="6104397"/>
-          <a:ext cx="425543" cy="319025"/>
+          <a:off x="0" y="0"/>
+          <a:ext cx="500000" cy="400000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3349,33 +3379,21 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="18" name="図 17">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId id="{E718EC42-FC80-BBC6-E3E7-9C99A042D2B0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="102" name="秋装飾_月"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId20" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
+        <a:blip r:embed="rId36" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2209179" y="6121946"/>
-          <a:ext cx="416291" cy="313382"/>
+          <a:off x="0" y="0"/>
+          <a:ext cx="500000" cy="400000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3399,33 +3417,21 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="24" name="図 23">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId id="{8D07C8FF-D1C4-1322-ECE3-D3E19681F34C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="103" name="秋装飾_月見"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId21" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
+        <a:blip r:embed="rId37" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3647971" y="6087211"/>
-          <a:ext cx="388248" cy="289423"/>
+          <a:off x="0" y="0"/>
+          <a:ext cx="500000" cy="400000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3449,33 +3455,21 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="26" name="図 25">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId id="{6336E3B8-D931-EFA8-9A59-8F7967C47D2A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="104" name="秋装飾_星"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId22" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
+        <a:blip r:embed="rId38" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5963944" y="6089230"/>
-          <a:ext cx="423759" cy="319004"/>
+          <a:off x="0" y="0"/>
+          <a:ext cx="500000" cy="400000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3499,48 +3493,25 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="56" name="図 55" descr="6月・梅雨・紫陽花・手書き風のデザイン（かわいいイラストのフレーム・はがき）の素材となりま">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId id="{04C2981B-9091-C7B8-35E9-5A2AEFB3E5BC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="105" name="秋フレーム_1"/>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
-      <xdr:blipFill rotWithShape="1">
-        <a:blip r:embed="rId30" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect b="81374"/>
+      <xdr:blipFill>
+        <a:blip r:embed="rId39" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
+      <xdr:spPr>
         <a:xfrm>
-          <a:off x="3434412" y="9628553"/>
-          <a:ext cx="2192874" cy="289296"/>
+          <a:off x="0" y="0"/>
+          <a:ext cx="500000" cy="400000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill>
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -3560,48 +3531,25 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="60" name="図 59" descr="6月・梅雨・紫陽花・手書き風のデザイン（かわいいイラストのフレーム・はがき）の素材となりま">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId id="{CE722464-239F-E42D-AF74-B20E84E95F16}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="106" name="秋フレーム_2"/>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
-      <xdr:blipFill rotWithShape="1">
-        <a:blip r:embed="rId31" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect b="81374"/>
+      <xdr:blipFill>
+        <a:blip r:embed="rId39" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
+      <xdr:spPr>
         <a:xfrm>
-          <a:off x="107578" y="9625228"/>
-          <a:ext cx="2199057" cy="289296"/>
+          <a:off x="0" y="0"/>
+          <a:ext cx="500000" cy="400000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill>
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -3621,48 +3569,25 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="62" name="図 61" descr="6月・梅雨・紫陽花・手書き風のデザイン（かわいいイラストのフレーム・はがき）の素材となりま">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId id="{6BDC1DDC-E28B-1F9A-46B3-58928C88815A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="107" name="秋フレーム_3"/>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
-      <xdr:blipFill rotWithShape="1">
-        <a:blip r:embed="rId32" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect t="1" r="65076" b="81610"/>
+      <xdr:blipFill>
+        <a:blip r:embed="rId39" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
+      <xdr:spPr>
         <a:xfrm>
-          <a:off x="2270853" y="9639294"/>
-          <a:ext cx="763622" cy="285640"/>
+          <a:off x="0" y="0"/>
+          <a:ext cx="500000" cy="400000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill>
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -3682,48 +3607,367 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="63" name="図 62" descr="6月・梅雨・紫陽花・手書き風のデザイン（かわいいイラストのフレーム・はがき）の素材となりま">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId id="{F7AA8125-F3AF-6660-DB30-D367D303A0B8}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="108" name="秋フレーム_4"/>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
-      <xdr:blipFill rotWithShape="1">
-        <a:blip r:embed="rId33" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect t="1" r="83445" b="82914"/>
+      <xdr:blipFill>
+        <a:blip r:embed="rId39" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
+      <xdr:spPr>
         <a:xfrm>
-          <a:off x="5642046" y="9653746"/>
-          <a:ext cx="361989" cy="265392"/>
+          <a:off x="0" y="0"/>
+          <a:ext cx="500000" cy="400000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill>
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>80000</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>30000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>880000</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>470000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="109" name="イラスト_リズム遊び"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId40" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="500000" cy="400000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>60000</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>30000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>870000</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>470000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="110" name="イラスト_秋の自然観察"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId41" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="500000" cy="400000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>80000</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>30000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>880000</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>470000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="111" name="イラスト_防災週間"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId42" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="500000" cy="400000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>60000</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>30000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>870000</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>470000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="112" name="イラスト_芋掘り"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId43" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="500000" cy="400000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>80000</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>30000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>880000</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>470000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="113" name="イラスト_敬老の日"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId44" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="500000" cy="400000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>60000</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>30000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>870000</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>470000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="114" name="イラスト_おはぎ"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId45" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="500000" cy="400000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>80000</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>30000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>880000</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>470000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="115" name="イラスト_お月見"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId46" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="500000" cy="400000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>60000</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>30000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>870000</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>470000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="116" name="イラスト_アスレチック"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId47" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="500000" cy="400000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>80000</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>30000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>880000</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>470000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="117" name="イラスト_ボッチャ"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId48" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="500000" cy="400000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
